--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484880_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484880_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. MARTI GONZALEZ</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0165</v>
+        <v>0.418</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6173999999999999</v>
+        <v>2.3763</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6339</v>
+        <v>-1.9583</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1722</v>
+        <v>-0.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0423</v>
+        <v>-1.3938</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1299</v>
+        <v>1.3638</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6762</v>
+        <v>2.5767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6762</v>
+        <v>1.062</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.5148</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.504</v>
+        <v>-2.6067</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6339</v>
+        <v>-2.4558</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1299</v>
+        <v>-0.1509</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1887</v>
+        <v>-1.3634</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0588</v>
+        <v>-0.7474</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1299</v>
+        <v>-0.616</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. HERNANDEZ TORRO</t>
+          <t>F. MARTI GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>A. HERNANDEZ TORRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3249</v>
+        <v>-0.0165</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7127</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0377</v>
+        <v>-0.6339</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.03</v>
+        <v>0.1722</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3938</v>
+        <v>0.0423</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3638</v>
+        <v>0.1299</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5767</v>
+        <v>0.6762</v>
       </c>
       <c r="K4" t="n">
-        <v>1.062</v>
+        <v>0.6762</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5148</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6067</v>
+        <v>-0.504</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4558</v>
+        <v>-0.6339</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1509</v>
+        <v>0.1299</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1062</v>
+        <v>-0.1887</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4109</v>
+        <v>-0.0588</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6953</v>
+        <v>-0.1299</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>G. ESQUEMBRE MORUGAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3443</v>
+        <v>-0.327</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5658</v>
+        <v>0.4788</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.9101</v>
+        <v>-0.8058</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6824</v>
+        <v>-0.1025</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3403</v>
+        <v>0.2598</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1385</v>
+        <v>0.4015</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0408</v>
+        <v>0.4015</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0976</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4806</v>
+        <v>-0.2442</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7233</v>
+        <v>-0.504</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7574</v>
+        <v>0.2598</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8658</v>
+        <v>-0.1825</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0692</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2034</v>
+        <v>-0.2598</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7922</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. ESQUEMBRE MORUGAN</t>
+          <t>M. PICO HINOJOSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5219</v>
+        <v>-1.273</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2839</v>
+        <v>-0.0165</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8058</v>
+        <v>-1.2565</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1573</v>
+        <v>-0.4617</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1025</v>
+        <v>-0.5916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2598</v>
+        <v>0.1299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4015</v>
+        <v>0.0423</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4015</v>
+        <v>0.0423</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2442</v>
+        <v>-0.504</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.504</v>
+        <v>-0.6339</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2598</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1176</v>
+        <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2598</v>
+        <v>-0.1299</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PICO HINOJOSA</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.273</v>
+        <v>-1.8915</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0165</v>
+        <v>3.1245</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2565</v>
+        <v>-5.0159</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4617</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5916</v>
+        <v>-0.6824</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1299</v>
+        <v>1.3403</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0423</v>
+        <v>3.1385</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0423</v>
+        <v>1.0408</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.0976</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.504</v>
+        <v>-2.4806</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6339</v>
+        <v>-1.7233</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1299</v>
+        <v>-0.7574</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1887</v>
+        <v>0.3186</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0588</v>
+        <v>0.6278</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1299</v>
+        <v>-0.3092</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6226</v>
+        <v>-1.547</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6226</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0762</v>
+        <v>-1.9199</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6931</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>-1.3831</v>
@@ -1078,10 +1078,10 @@
         <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8847</v>
+        <v>-0.7285</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2352</v>
+        <v>-0.0789</v>
       </c>
       <c r="U8" t="n">
         <v>-0.6496</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>A. FERRIZ SELLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8415</v>
+        <v>-2.3174</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1229</v>
+        <v>-1.0075</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7186</v>
+        <v>-1.31</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0164</v>
+        <v>-1.1835</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8322</v>
+        <v>-1.9369</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8487</v>
+        <v>0.7534</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4776</v>
+        <v>0.8334</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1275</v>
+        <v>0.4703</v>
       </c>
       <c r="L9" t="n">
-        <v>3.35</v>
+        <v>0.3631</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4611</v>
+        <v>-2.017</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.9597</v>
+        <v>-2.4072</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4986</v>
+        <v>0.3903</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.1514</v>
+        <v>0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0384</v>
+        <v>-1.1322</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5554</v>
+        <v>-1.2095</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4109</v>
+        <v>-0.7087</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1445</v>
+        <v>-0.5008</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8488</v>
+        <v>-0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1845</v>
+        <v>-2.4328</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3261</v>
+        <v>-1.2645</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1416</v>
+        <v>-1.1683</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0906</v>
+        <v>1.0164</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5095</v>
+        <v>-2.8322</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6001</v>
+        <v>3.8487</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2339</v>
+        <v>3.4776</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0197</v>
+        <v>0.1275</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2142</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1433</v>
+        <v>-2.4611</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5292</v>
+        <v>-2.9597</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3859</v>
+        <v>0.4986</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.8305</v>
+        <v>-4.1514</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.1514</v>
+        <v>-6.0384</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5202</v>
+        <v>-1.1467</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4086</v>
+        <v>-0.5525</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1116</v>
+        <v>-0.5942</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9244</v>
+        <v>1.8488</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3144</v>
+        <v>-3.4303</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2284</v>
+        <v>-1.3443</v>
       </c>
       <c r="F11" t="n">
         <v>-2.086</v>
@@ -1312,10 +1312,10 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0146</v>
+        <v>-1.1306</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2881</v>
+        <v>-0.4041</v>
       </c>
       <c r="U11" t="n">
         <v>-0.7265</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. FERRIZ SELLES</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5487</v>
+        <v>-3.4793</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7097</v>
+        <v>-3.4622</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.839</v>
+        <v>-0.0171</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1835</v>
+        <v>1.0906</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9369</v>
+        <v>-0.5095</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7534</v>
+        <v>1.6001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8334</v>
+        <v>1.2339</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4703</v>
+        <v>1.0197</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3631</v>
+        <v>0.2142</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.017</v>
+        <v>-0.1433</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4072</v>
+        <v>-1.5292</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3903</v>
+        <v>1.3859</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3774</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1322</v>
+        <v>-4.1514</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4408</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4109</v>
+        <v>-0.5447</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0299</v>
+        <v>-0.2703</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3018</v>
+        <v>-0.9244</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3018</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.737</v>
+        <v>-5.6312</v>
       </c>
       <c r="E13" t="n">
         <v>-3.3767</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3603</v>
+        <v>-2.2545</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6355</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3656</v>
+        <v>-0.2598</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2939</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0717</v>
+        <v>0.0341</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8488</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.1994</v>
+        <v>-22.3174</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6762</v>
+        <v>-3.794100000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-18.5233</v>
@@ -1546,13 +1546,13 @@
         <v>9.435</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.965199999999999</v>
+        <v>-7.083500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6833</v>
+        <v>-2.8015</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.282</v>
+        <v>-4.281999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-3.075</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5759</v>
+        <v>5.7695</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8569</v>
+        <v>5.7595</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.281</v>
+        <v>0.01</v>
       </c>
       <c r="G15" t="n">
         <v>1.4943</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3268</v>
+        <v>0.5204</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5937</v>
+        <v>0.4962</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2669</v>
+        <v>0.0241</v>
       </c>
       <c r="V15" t="n">
         <v>1.8678</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2342</v>
+        <v>4.2696</v>
       </c>
       <c r="E16" t="n">
-        <v>2.022</v>
+        <v>1.2426</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2122</v>
+        <v>3.027</v>
       </c>
       <c r="G16" t="n">
         <v>0.3261</v>
@@ -1702,13 +1702,13 @@
         <v>3.2079</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7194</v>
+        <v>1.7547</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5524</v>
+        <v>0.7729</v>
       </c>
       <c r="U16" t="n">
-        <v>1.167</v>
+        <v>0.9818</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2962</v>
+        <v>3.473</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8559</v>
+        <v>3.9533</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5597</v>
+        <v>-0.4804</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3307</v>
@@ -1780,13 +1780,13 @@
         <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3251</v>
+        <v>0.5019</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4732</v>
+        <v>0.5706</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1481</v>
+        <v>-0.0688</v>
       </c>
       <c r="V17" t="n">
         <v>2.1696</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8513</v>
+        <v>3.0821</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5325</v>
+        <v>2.5148</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3189</v>
+        <v>0.5673</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3412</v>
+        <v>4.1083</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0621</v>
+        <v>3.7322</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7209</v>
+        <v>0.3762</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6516</v>
+        <v>5.2775</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1607</v>
+        <v>3.4082</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5091</v>
+        <v>1.8694</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3104</v>
+        <v>-1.1692</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.324</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2118</v>
+        <v>-1.4932</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6983</v>
+        <v>-1.887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3774</v>
+        <v>-4.1514</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8118</v>
+        <v>0.8608</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0436</v>
+        <v>0.1435</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8554</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4245</v>
+        <v>3.0294</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1767</v>
+        <v>1.9222</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7523</v>
+        <v>1.1073</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2043</v>
+        <v>0.3412</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7843</v>
+        <v>2.0621</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.58</v>
+        <v>-1.7209</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5902</v>
+        <v>1.6516</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5902</v>
+        <v>2.1607</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.5091</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3859</v>
+        <v>-1.3104</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1941</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.58</v>
+        <v>-1.2118</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.3774</v>
       </c>
       <c r="R19" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9557</v>
+        <v>0.9899</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9639</v>
+        <v>0.3462</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.6438</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1426</v>
+        <v>1.7274</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4431</v>
+        <v>-0.441</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6995</v>
+        <v>2.1684</v>
       </c>
       <c r="G20" t="n">
-        <v>4.1083</v>
+        <v>0.3217</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7322</v>
+        <v>3.2791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3762</v>
+        <v>-2.9574</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2775</v>
+        <v>0.9022</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4082</v>
+        <v>3.4919</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8694</v>
+        <v>-2.5897</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1692</v>
+        <v>-0.5805</v>
       </c>
       <c r="N20" t="n">
-        <v>0.324</v>
+        <v>-0.2128</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4932</v>
+        <v>-0.3676</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1514</v>
+        <v>-3.0192</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>1.1229</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9283</v>
+        <v>0.4498</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8495</v>
+        <v>0.6732</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2452</v>
+        <v>1.2262</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9835</v>
+        <v>1.6882</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3436</v>
+        <v>2.2024</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3271</v>
+        <v>-0.5142</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3217</v>
+        <v>0.2043</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2791</v>
+        <v>1.7843</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9574</v>
+        <v>-1.58</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9022</v>
+        <v>1.5902</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4919</v>
+        <v>1.5902</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5897</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5805</v>
+        <v>-1.3859</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2128</v>
+        <v>0.1941</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3676</v>
+        <v>-1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0192</v>
+        <v>-0.3774</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3791</v>
+        <v>1.2195</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5472</v>
+        <v>0.9896</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8319</v>
+        <v>0.2299</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2262</v>
+        <v>-1.2452</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5318</v>
+        <v>1.5053</v>
       </c>
       <c r="E22" t="n">
         <v>1.5721</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0403</v>
+        <v>-0.0668</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3499</v>
@@ -2170,13 +2170,13 @@
         <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1834</v>
+        <v>0.1569</v>
       </c>
       <c r="T22" t="n">
         <v>0.238</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0546</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4239</v>
+        <v>-0.2736</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4465</v>
       </c>
       <c r="F23" t="n">
-        <v>0.12</v>
+        <v>0.1729</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8366</v>
@@ -2248,13 +2248,13 @@
         <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0353</v>
+        <v>0.1856</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.0974</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4167</v>
+        <v>-1.0714</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0484</v>
+        <v>0.2439</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3682</v>
+        <v>-1.3153</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5546</v>
@@ -2326,13 +2326,13 @@
         <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3074</v>
+        <v>0.6526</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1147</v>
+        <v>0.1776</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4221</v>
+        <v>0.475</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>23.1994</v>
+        <v>23.1995</v>
       </c>
       <c r="E25" t="n">
         <v>18.5233</v>
@@ -2404,19 +2404,19 @@
         <v>18.87</v>
       </c>
       <c r="S25" t="n">
-        <v>7.9653</v>
+        <v>7.9652</v>
       </c>
       <c r="T25" t="n">
         <v>4.2818</v>
       </c>
       <c r="U25" t="n">
-        <v>3.6834</v>
+        <v>3.6833</v>
       </c>
       <c r="V25" t="n">
         <v>3.075</v>
       </c>
       <c r="W25" t="n">
-        <v>8.036799999999999</v>
+        <v>8.036800000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-4.9618</v>
